--- a/artfynd/A 44052-2021 artfynd.xlsx
+++ b/artfynd/A 44052-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,6 +793,391 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>121691937</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57898</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Dammkärrsmossen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>516335</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6585781</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Axberg</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Engla Grönvall</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Alight  - Dylta bruk 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121690862</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57726</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Dammkärrsmossen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>516323</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6585754</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Axberg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-06-06</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>06:29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-06-06</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>06:29</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Angelia Ellvin</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Alight  - Dylta bruk 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121692875</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58034</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Dammkärrsmossen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>516258</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6585731</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Axberg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-06-06</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>06:14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-06-06</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>06:14</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Angelia Ellvin</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Alight  - Dylta bruk 2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 44052-2021 artfynd.xlsx
+++ b/artfynd/A 44052-2021 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121692875</v>
+        <v>121691937</v>
       </c>
       <c r="B3" t="n">
-        <v>58034</v>
+        <v>57898</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,16 +811,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>102990</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -830,17 +830,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -849,13 +849,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516258</v>
+        <v>516335</v>
       </c>
       <c r="R3" t="n">
-        <v>6585731</v>
+        <v>6585781</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,22 +879,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>06:14</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>06:14</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,7 +914,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1050,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121691937</v>
+        <v>121692875</v>
       </c>
       <c r="B5" t="n">
-        <v>57898</v>
+        <v>58034</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,16 +1066,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102990</v>
+        <v>103044</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1085,17 +1085,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1104,13 +1104,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516335</v>
+        <v>516258</v>
       </c>
       <c r="R5" t="n">
-        <v>6585781</v>
+        <v>6585731</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1134,22 +1134,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>06:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>06:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 44052-2021 artfynd.xlsx
+++ b/artfynd/A 44052-2021 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121691937</v>
+        <v>121692875</v>
       </c>
       <c r="B3" t="n">
-        <v>57898</v>
+        <v>58034</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,16 +811,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102990</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -830,17 +830,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -849,13 +849,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516335</v>
+        <v>516258</v>
       </c>
       <c r="R3" t="n">
-        <v>6585781</v>
+        <v>6585731</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,22 +879,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>06:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>06:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,7 +914,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1050,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121692875</v>
+        <v>121691937</v>
       </c>
       <c r="B5" t="n">
-        <v>58034</v>
+        <v>57898</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,16 +1066,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103044</v>
+        <v>102990</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1085,17 +1085,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1104,13 +1104,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516258</v>
+        <v>516335</v>
       </c>
       <c r="R5" t="n">
-        <v>6585731</v>
+        <v>6585781</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1134,22 +1134,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>06:14</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>06:14</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 44052-2021 artfynd.xlsx
+++ b/artfynd/A 44052-2021 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121692875</v>
+        <v>121690862</v>
       </c>
       <c r="B3" t="n">
-        <v>58034</v>
+        <v>57726</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,16 +811,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -830,17 +830,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>i par</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -849,13 +844,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516258</v>
+        <v>516323</v>
       </c>
       <c r="R3" t="n">
-        <v>6585731</v>
+        <v>6585754</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,7 +879,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>06:14</t>
+          <t>06:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +889,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>06:14</t>
+          <t>06:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121690862</v>
+        <v>121691937</v>
       </c>
       <c r="B4" t="n">
-        <v>57726</v>
+        <v>57898</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -941,16 +936,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>102990</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -963,9 +958,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -974,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516323</v>
+        <v>516335</v>
       </c>
       <c r="R4" t="n">
-        <v>6585754</v>
+        <v>6585781</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1004,22 +1004,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>06:29</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>06:29</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1050,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121691937</v>
+        <v>121692875</v>
       </c>
       <c r="B5" t="n">
-        <v>57898</v>
+        <v>58034</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,16 +1066,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102990</v>
+        <v>103044</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1085,17 +1085,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1104,13 +1104,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516335</v>
+        <v>516258</v>
       </c>
       <c r="R5" t="n">
-        <v>6585781</v>
+        <v>6585731</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1134,22 +1134,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>06:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>06:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 44052-2021 artfynd.xlsx
+++ b/artfynd/A 44052-2021 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121690862</v>
+        <v>121692875</v>
       </c>
       <c r="B3" t="n">
-        <v>57726</v>
+        <v>58034</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,16 +811,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -830,12 +830,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>i par</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -844,13 +849,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516323</v>
+        <v>516258</v>
       </c>
       <c r="R3" t="n">
-        <v>6585754</v>
+        <v>6585731</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>06:29</t>
+          <t>06:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>06:29</t>
+          <t>06:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121691937</v>
+        <v>121690862</v>
       </c>
       <c r="B4" t="n">
-        <v>57898</v>
+        <v>57726</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,16 +941,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102990</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -958,14 +963,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -974,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516335</v>
+        <v>516323</v>
       </c>
       <c r="R4" t="n">
-        <v>6585781</v>
+        <v>6585754</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1004,22 +1004,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>06:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>06:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1050,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121692875</v>
+        <v>121691937</v>
       </c>
       <c r="B5" t="n">
-        <v>58034</v>
+        <v>57898</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,16 +1066,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103044</v>
+        <v>102990</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1085,17 +1085,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1104,13 +1104,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516258</v>
+        <v>516335</v>
       </c>
       <c r="R5" t="n">
-        <v>6585731</v>
+        <v>6585781</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1134,22 +1134,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>06:14</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>06:14</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 44052-2021 artfynd.xlsx
+++ b/artfynd/A 44052-2021 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121692875</v>
+        <v>121690862</v>
       </c>
       <c r="B3" t="n">
-        <v>58034</v>
+        <v>57726</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,16 +811,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -830,17 +830,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>i par</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -849,13 +844,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516258</v>
+        <v>516323</v>
       </c>
       <c r="R3" t="n">
-        <v>6585731</v>
+        <v>6585754</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,7 +879,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>06:14</t>
+          <t>06:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +889,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>06:14</t>
+          <t>06:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121690862</v>
+        <v>121692875</v>
       </c>
       <c r="B4" t="n">
-        <v>57726</v>
+        <v>58034</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -941,16 +936,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -960,12 +955,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>i par</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -974,13 +974,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516323</v>
+        <v>516258</v>
       </c>
       <c r="R4" t="n">
-        <v>6585754</v>
+        <v>6585731</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>06:29</t>
+          <t>06:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>06:29</t>
+          <t>06:14</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 44052-2021 artfynd.xlsx
+++ b/artfynd/A 44052-2021 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>121690862</v>
       </c>
       <c r="B3" t="n">
-        <v>57726</v>
+        <v>57734</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>121692875</v>
       </c>
       <c r="B4" t="n">
-        <v>58034</v>
+        <v>58042</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>121691937</v>
       </c>
       <c r="B5" t="n">
-        <v>57898</v>
+        <v>57906</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 44052-2021 artfynd.xlsx
+++ b/artfynd/A 44052-2021 artfynd.xlsx
@@ -920,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121692875</v>
+        <v>121691937</v>
       </c>
       <c r="B4" t="n">
-        <v>58042</v>
+        <v>57906</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,16 +936,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>102990</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -955,17 +955,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -974,13 +974,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516258</v>
+        <v>516335</v>
       </c>
       <c r="R4" t="n">
-        <v>6585731</v>
+        <v>6585781</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1004,22 +1004,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>06:14</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>06:14</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1050,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121691937</v>
+        <v>121692875</v>
       </c>
       <c r="B5" t="n">
-        <v>57906</v>
+        <v>58042</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,16 +1066,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102990</v>
+        <v>103044</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1085,17 +1085,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1104,13 +1104,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516335</v>
+        <v>516258</v>
       </c>
       <c r="R5" t="n">
-        <v>6585781</v>
+        <v>6585731</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1134,22 +1134,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>06:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>06:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 44052-2021 artfynd.xlsx
+++ b/artfynd/A 44052-2021 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121690862</v>
+        <v>121692875</v>
       </c>
       <c r="B3" t="n">
-        <v>57734</v>
+        <v>58046</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,16 +811,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -830,12 +830,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>i par</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -844,13 +849,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516323</v>
+        <v>516258</v>
       </c>
       <c r="R3" t="n">
-        <v>6585754</v>
+        <v>6585731</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>06:29</t>
+          <t>06:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>06:29</t>
+          <t>06:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121691937</v>
+        <v>121690862</v>
       </c>
       <c r="B4" t="n">
-        <v>57906</v>
+        <v>57738</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,16 +941,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102990</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -958,14 +963,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -974,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516335</v>
+        <v>516323</v>
       </c>
       <c r="R4" t="n">
-        <v>6585781</v>
+        <v>6585754</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1004,22 +1004,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>06:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>06:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1050,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121692875</v>
+        <v>121691937</v>
       </c>
       <c r="B5" t="n">
-        <v>58042</v>
+        <v>57910</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,16 +1066,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103044</v>
+        <v>102990</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1085,17 +1085,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1104,13 +1104,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516258</v>
+        <v>516335</v>
       </c>
       <c r="R5" t="n">
-        <v>6585731</v>
+        <v>6585781</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1134,22 +1134,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>06:14</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>06:14</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 44052-2021 artfynd.xlsx
+++ b/artfynd/A 44052-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1178,6 +1178,123 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122587137</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57399</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Dammkärrsmossen, Dylta bruk, Ölmbrotorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>516242</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6585848</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Axberg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2019-07-24</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2019-07-24</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sara Elg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sara Elg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 44052-2021 artfynd.xlsx
+++ b/artfynd/A 44052-2021 artfynd.xlsx
@@ -1183,7 +1183,7 @@
         <v>122587137</v>
       </c>
       <c r="B6" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
